--- a/docs/package/05_Delivery/Upload_Templates/Dealer_Sales_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Dealer_Sales_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="139">
   <si>
     <t xml:space="preserve">Dealer Branch Code</t>
   </si>
@@ -372,12 +372,6 @@
     <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Dealer Programmes &gt; Dealer Sales Upload</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/motor-programmes/:id/sales/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -432,10 +426,10 @@
     <t xml:space="preserve">A financed sale names the bank (or the programme's bank applies when there is a loan amount): the bank is the mortgagee on the policy and the bank endorsement letter can be printed from the sale.</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -443,9 +437,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -483,6 +477,26 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -564,9 +578,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -592,6 +606,8 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1272,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -1368,29 +1384,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="0" t="s">
+      <c r="B12" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="14">
       <c r="B14" s="4" t="s">
         <v>138</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Dealer_Sales_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Dealer_Sales_Upload_Template.xlsx
@@ -369,7 +369,7 @@
     <t xml:space="preserve">Upload on</t>
   </si>
   <si>
-    <t xml:space="preserve">Operations &gt; Sales &amp; Marketing &gt; Dealer Programmes &gt; Dealer Sales Upload</t>
+    <t xml:space="preserve">Sales &amp; Placement &gt; Dealer Programmes &gt; Dealer Sales Upload</t>
   </si>
   <si>
     <t xml:space="preserve">File types</t>
